--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -1423,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113028464</v>
+        <v>113028503</v>
       </c>
       <c r="B8" t="n">
-        <v>55826</v>
+        <v>56781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,20 +1435,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100045</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,16 +1458,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1547,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113028511</v>
+        <v>113028521</v>
       </c>
       <c r="B9" t="n">
-        <v>56892</v>
+        <v>57182</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,16 +1559,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205976</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1582,7 +1578,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1667,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113028503</v>
+        <v>113028464</v>
       </c>
       <c r="B10" t="n">
-        <v>56781</v>
+        <v>55826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1679,20 +1675,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1702,12 +1698,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113028521</v>
+        <v>113028511</v>
       </c>
       <c r="B11" t="n">
-        <v>57182</v>
+        <v>56892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>205976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>

--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>113298332</v>
       </c>
       <c r="B12" t="n">
-        <v>55984</v>
+        <v>55985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>113298332</v>
       </c>
       <c r="B12" t="n">
-        <v>55985</v>
+        <v>55988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>113298332</v>
       </c>
       <c r="B12" t="n">
-        <v>55988</v>
+        <v>55992</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>113298332</v>
       </c>
       <c r="B12" t="n">
-        <v>55992</v>
+        <v>55999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">

--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,6 +2158,130 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125279478</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57454</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hagen, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>371512</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6414708</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Nyberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Nyberg, Per Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 67271-2020 artfynd.xlsx
+++ b/artfynd/A 67271-2020 artfynd.xlsx
@@ -2163,7 +2163,7 @@
         <v>125279478</v>
       </c>
       <c r="B14" t="n">
-        <v>57454</v>
+        <v>57471</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
